--- a/administrative_forms/018_fire_safety_inspection_report_form--administrative_forms.xlsx
+++ b/administrative_forms/018_fire_safety_inspection_report_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fire_extinguishing_systems</t>
+          <t>fire extinguishing systems</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fire_safety_equipment</t>
+          <t>fire safety equipment</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fire_safety_signs</t>
+          <t>fire safety signs</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fire_exit_routes</t>
+          <t>fire exit routes</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fire_drills</t>
+          <t>fire drills</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fire_safety_plan</t>
+          <t>fire safety plan</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fire_safety_training</t>
+          <t>fire safety training</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>emergency_exit_plan</t>
+          <t>emergency exit plan</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fire_hazards</t>
+          <t>fire hazards</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>emergency_contact_numbers</t>
+          <t>emergency contact numbers</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fire_safety_equipment_testing</t>
+          <t>fire safety equipment testing</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>not working</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>needs_repair</t>
+          <t>needs repair</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>needs_inspection</t>
+          <t>needs inspection</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>not required</t>
         </is>
       </c>
     </row>
